--- a/artfynd/A 46391-2024 artfynd.xlsx
+++ b/artfynd/A 46391-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>374784</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609808.5540028166</v>
+        <v>609809</v>
       </c>
       <c r="R2" t="n">
-        <v>7165492.500336885</v>
+        <v>7165493</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,474 +774,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1569313</v>
-      </c>
-      <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Stormyran-Kvisselmyran strax norr om Hacksjön, myrholme, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>609704.6120956145</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7165713.089235661</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1569315</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Stormyran-Kvisselmyran strax norr om Hacksjön, myrholme, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>609810.9360550157</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7165450.465469424</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1569314</v>
-      </c>
-      <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Stormyran-Kvisselmyran strax norr om Hacksjön, myrholme, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>609673.757646499</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7165685.757458958</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1569316</v>
-      </c>
-      <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Stormyran-Kvisselmyran strax norr om Hacksjön, myrholme, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>609826.7525010981</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7164977.780419916</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2012-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
